--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N87_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N87_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.0825347381084</v>
+        <v>5.213411894942615</v>
       </c>
       <c r="D2" t="n">
-        <v>29.63466965814956</v>
+        <v>4.815633819449303</v>
       </c>
       <c r="E2" t="n">
-        <v>13.48920449687909</v>
+        <v>2.191995730742853</v>
       </c>
       <c r="F2" t="n">
-        <v>14.76862045048855</v>
+        <v>2.39990082320439</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.20220120618612</v>
+        <v>4.745357696005244</v>
       </c>
       <c r="D3" t="n">
-        <v>29.94207353937274</v>
+        <v>4.86558695014807</v>
       </c>
       <c r="E3" t="n">
-        <v>13.48920449687909</v>
+        <v>2.191995730742853</v>
       </c>
       <c r="F3" t="n">
-        <v>14.76862045048855</v>
+        <v>2.39990082320439</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.61823361855954</v>
+        <v>3.512962963015925</v>
       </c>
       <c r="D4" t="n">
-        <v>23.71300538429365</v>
+        <v>3.853363374947719</v>
       </c>
       <c r="E4" t="n">
-        <v>13.48920449687909</v>
+        <v>2.191995730742853</v>
       </c>
       <c r="F4" t="n">
-        <v>14.76862045048855</v>
+        <v>2.39990082320439</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.60508074247556</v>
+        <v>3.510825620652279</v>
       </c>
       <c r="D5" t="n">
-        <v>17.84656829757475</v>
+        <v>2.900067348355897</v>
       </c>
       <c r="E5" t="n">
-        <v>13.48920449687909</v>
+        <v>2.191995730742853</v>
       </c>
       <c r="F5" t="n">
-        <v>14.76862045048855</v>
+        <v>2.39990082320439</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>13.62913994313016</v>
+        <v>2.21473524075865</v>
       </c>
       <c r="D6" t="n">
-        <v>5.032502301844866</v>
+        <v>0.8177816240497907</v>
       </c>
       <c r="E6" t="n">
-        <v>13.48920449687909</v>
+        <v>2.191995730742853</v>
       </c>
       <c r="F6" t="n">
-        <v>14.76862045048855</v>
+        <v>2.39990082320439</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.86662802356586</v>
+        <v>2.740827053829453</v>
       </c>
       <c r="D7" t="n">
-        <v>7.33591074235184</v>
+        <v>1.192085495632174</v>
       </c>
       <c r="E7" t="n">
-        <v>13.48920449687909</v>
+        <v>2.191995730742853</v>
       </c>
       <c r="F7" t="n">
-        <v>14.76862045048855</v>
+        <v>2.39990082320439</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.20103454847555</v>
+        <v>1.820168114127277</v>
       </c>
       <c r="D8" t="n">
-        <v>11.35677011702936</v>
+        <v>1.845475144017272</v>
       </c>
       <c r="E8" t="n">
-        <v>13.48920449687909</v>
+        <v>2.191995730742853</v>
       </c>
       <c r="F8" t="n">
-        <v>14.76862045048855</v>
+        <v>2.39990082320439</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.30195448268423</v>
+        <v>9.149067603436189</v>
       </c>
       <c r="D9" t="n">
-        <v>53.42917706210571</v>
+        <v>8.682241272592178</v>
       </c>
       <c r="E9" t="n">
-        <v>13.48920449687909</v>
+        <v>2.191995730742853</v>
       </c>
       <c r="F9" t="n">
-        <v>14.76862045048855</v>
+        <v>2.39990082320439</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
